--- a/InputData/trans/VRSbRIC/Veh Revenue Share by Recipient ISIC Code.xlsx
+++ b/InputData/trans/VRSbRIC/Veh Revenue Share by Recipient ISIC Code.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\trans\VRSbRIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\VRSbRIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFABE065-4FE4-4AA3-B341-5EF8B4091819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF176CE5-A45B-4223-A7CC-90AA7923542E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23640" xr2:uid="{98104574-AC6C-45D3-B7DA-9D389A9BFE72}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="LDV Data" sheetId="4" r:id="rId2"/>
-    <sheet name="HDV Data" sheetId="5" r:id="rId3"/>
-    <sheet name="VRSbRIC" sheetId="3" r:id="rId4"/>
+    <sheet name="LDV Data" sheetId="2" r:id="rId2"/>
+    <sheet name="Checks" sheetId="3" r:id="rId3"/>
+    <sheet name="HDV Data" sheetId="4" r:id="rId4"/>
+    <sheet name="VRSbRIC" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="149">
   <si>
     <t>VRSbRIC Vehicle Revenue Share by Recipient ISIC Code</t>
   </si>
@@ -44,27 +45,90 @@
     <t>Sources:</t>
   </si>
   <si>
+    <t>Passenger LDVs</t>
+  </si>
+  <si>
+    <t>EPA</t>
+  </si>
+  <si>
+    <t>Automobile Industry Retail Price Equivalent and Indirect Cost Multipliers</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Table 3-3</t>
+  </si>
+  <si>
+    <t>Freight LDVs and HDVs and Passenger HDVs</t>
+  </si>
+  <si>
+    <t>Heavy Duty Truck Retail Price Equivalent and Indirect Cost Multipliers</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>We assume the same cost breakdowns for all technologies, but assign non-road to non-road vehicle manufacturing</t>
+  </si>
+  <si>
+    <t>The RPEF file also controls whether or not these values are used</t>
+  </si>
+  <si>
+    <t>42-code sibling (build_sector_shares_42):</t>
+  </si>
+  <si>
+    <t>This workbook is the 42-code (un-split) sibling of the 52-code expansion. The 42 scheme is the 52 scheme with the six OECD-native parents</t>
+  </si>
+  <si>
+    <t>left merged (ISIC 01T03, 07T08, 30, 49T53, 69T82, 90T96); the BEA carves ISIC 231/239 and 351/352T353 are retained (present in both</t>
+  </si>
+  <si>
+    <t>schemes).</t>
+  </si>
+  <si>
+    <t>The output tabs are the stock derivation, unchanged and live: the stock workbook is natively 42-code (its output columns already are the</t>
+  </si>
+  <si>
+    <t>42-code ISIC list, in canonical order), so no child split is applied here. The motorbike row is corrected to match LDVs: the stock file</t>
+  </si>
+  <si>
+    <t>(4.0.6 and 4.1) pointed its ISIC 45T47 cell at the HDV dealer share, so the row summed to 0.890 instead of 1 (user decision 2026-07-20).</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
     <t>Industy Average Total</t>
   </si>
   <si>
+    <t>Industry Average RPE Only</t>
+  </si>
+  <si>
+    <t>ISIC Code</t>
+  </si>
+  <si>
     <t>Vehicle Manufacturing</t>
   </si>
   <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
     <t>Cost of Sales</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Production Overhead</t>
   </si>
   <si>
     <t>Warranty</t>
   </si>
   <si>
+    <t>ISIC 29</t>
+  </si>
+  <si>
     <t>R&amp;D (product dev)</t>
   </si>
   <si>
@@ -92,6 +156,9 @@
     <t>Transportation</t>
   </si>
   <si>
+    <t>ISIC 45T47</t>
+  </si>
+  <si>
     <t>Marketing</t>
   </si>
   <si>
@@ -107,138 +174,249 @@
     <t>Other</t>
   </si>
   <si>
+    <t>Net income</t>
+  </si>
+  <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Industry Average RPE Only</t>
-  </si>
-  <si>
-    <t>ISIC Code</t>
+    <t>ISIC 01T03</t>
   </si>
   <si>
     <t>{Agriculture, forestry and fishing}</t>
   </si>
   <si>
+    <t>ISIC 05</t>
+  </si>
+  <si>
     <t>{Coal mining}</t>
   </si>
   <si>
+    <t>ISIC 06</t>
+  </si>
+  <si>
     <t>{Oil and gas extraction}</t>
   </si>
   <si>
+    <t>ISIC 07T08</t>
+  </si>
+  <si>
     <t>{Mining and quarrying of non-energy producing products}</t>
   </si>
   <si>
+    <t>ISIC 09</t>
+  </si>
+  <si>
     <t>{Mining support service activities}</t>
   </si>
   <si>
+    <t>ISIC 10T12</t>
+  </si>
+  <si>
     <t>{Food products, beverages and tobacco}</t>
   </si>
   <si>
+    <t>ISIC 13T15</t>
+  </si>
+  <si>
     <t>{Textiles, wearing apparel, leather and related products}</t>
   </si>
   <si>
+    <t>ISIC 16</t>
+  </si>
+  <si>
     <t>{Wood and of products of wood and cork (except furniture)}</t>
   </si>
   <si>
+    <t>ISIC 17T18</t>
+  </si>
+  <si>
     <t>{Paper products and printing}</t>
   </si>
   <si>
+    <t>ISIC 19</t>
+  </si>
+  <si>
     <t>{Coke and refined petroleum products}</t>
   </si>
   <si>
+    <t>ISIC 20</t>
+  </si>
+  <si>
     <t>{Chemicals}</t>
   </si>
   <si>
+    <t>ISIC 21</t>
+  </si>
+  <si>
     <t>{Pharmaceuticals}</t>
   </si>
   <si>
+    <t>ISIC 22</t>
+  </si>
+  <si>
     <t>{Rubber and plastics products}</t>
   </si>
   <si>
+    <t>ISIC 231</t>
+  </si>
+  <si>
     <t>{Glass}</t>
   </si>
   <si>
+    <t>ISIC 239</t>
+  </si>
+  <si>
     <t>{Cement and other non-metallic minerals}</t>
   </si>
   <si>
+    <t>ISIC 241</t>
+  </si>
+  <si>
     <t>{Iron and steel}</t>
   </si>
   <si>
+    <t>ISIC 242</t>
+  </si>
+  <si>
     <t>{Other metals}</t>
   </si>
   <si>
+    <t>ISIC 25</t>
+  </si>
+  <si>
     <t>{Fabricated metal products, except machinery and equipment}</t>
   </si>
   <si>
+    <t>ISIC 26</t>
+  </si>
+  <si>
     <t>{Computer, electronic and optical products}</t>
   </si>
   <si>
+    <t>ISIC 27</t>
+  </si>
+  <si>
     <t>{Electrical equipment}</t>
   </si>
   <si>
+    <t>ISIC 28</t>
+  </si>
+  <si>
     <t>{Machinery and equipment n.e.c.}</t>
   </si>
   <si>
     <t>{Motor vehicles, trailers and semi-trailers}</t>
   </si>
   <si>
+    <t>ISIC 30</t>
+  </si>
+  <si>
     <t>{Other transport equipment}</t>
   </si>
   <si>
+    <t>ISIC 31T33</t>
+  </si>
+  <si>
     <t>{Other manufacturing; repair and installation of machinery and equipment}</t>
   </si>
   <si>
+    <t>ISIC 351</t>
+  </si>
+  <si>
     <t>{Electricity generation and distribution}</t>
   </si>
   <si>
+    <t>ISIC 352T353</t>
+  </si>
+  <si>
     <t>{Energy pipelines and gas processing}</t>
   </si>
   <si>
+    <t>ISIC 36T39</t>
+  </si>
+  <si>
     <t>{Water and waste}</t>
   </si>
   <si>
+    <t>ISIC 41T43</t>
+  </si>
+  <si>
     <t>{Construction}</t>
   </si>
   <si>
     <t>{Wholesale and retail trade; repair of motor vehicles}</t>
   </si>
   <si>
+    <t>ISIC 49T53</t>
+  </si>
+  <si>
     <t>{Transportation and storage}</t>
   </si>
   <si>
+    <t>ISIC 55T56</t>
+  </si>
+  <si>
     <t>{Accomodation and food services}</t>
   </si>
   <si>
+    <t>ISIC 58T60</t>
+  </si>
+  <si>
     <t>{Publishing, audiovisual and broadcasting activities}</t>
   </si>
   <si>
+    <t>ISIC 61</t>
+  </si>
+  <si>
     <t>{Telecommunications}</t>
   </si>
   <si>
+    <t>ISIC 62T63</t>
+  </si>
+  <si>
     <t>{IT and other information services}</t>
   </si>
   <si>
+    <t>ISIC 64T66</t>
+  </si>
+  <si>
     <t>{Financial and insurance activities}</t>
   </si>
   <si>
+    <t>ISIC 68</t>
+  </si>
+  <si>
     <t>{Real estate activities}</t>
   </si>
   <si>
+    <t>ISIC 69T82</t>
+  </si>
+  <si>
     <t>{Other business sector services}</t>
   </si>
   <si>
+    <t>ISIC 84</t>
+  </si>
+  <si>
     <t>{Public administration and defence; compulsory social security}</t>
   </si>
   <si>
+    <t>ISIC 85</t>
+  </si>
+  <si>
     <t>{Education}</t>
   </si>
   <si>
+    <t>ISIC 86T88</t>
+  </si>
+  <si>
     <t>{Human health and social work}</t>
   </si>
   <si>
+    <t>ISIC 90T96</t>
+  </si>
+  <si>
     <t>{Arts, entertainment, recreation and other service activities}</t>
   </si>
   <si>
@@ -248,130 +426,43 @@
     <t>{Private households with employed persons}</t>
   </si>
   <si>
-    <t>ISIC 01T03</t>
-  </si>
-  <si>
-    <t>ISIC 05</t>
-  </si>
-  <si>
-    <t>ISIC 06</t>
-  </si>
-  <si>
-    <t>ISIC 07T08</t>
-  </si>
-  <si>
-    <t>ISIC 09</t>
-  </si>
-  <si>
-    <t>ISIC 10T12</t>
-  </si>
-  <si>
-    <t>ISIC 13T15</t>
-  </si>
-  <si>
-    <t>ISIC 16</t>
-  </si>
-  <si>
-    <t>ISIC 17T18</t>
-  </si>
-  <si>
-    <t>ISIC 19</t>
-  </si>
-  <si>
-    <t>ISIC 20</t>
-  </si>
-  <si>
-    <t>ISIC 21</t>
-  </si>
-  <si>
-    <t>ISIC 22</t>
-  </si>
-  <si>
-    <t>ISIC 231</t>
-  </si>
-  <si>
-    <t>ISIC 239</t>
-  </si>
-  <si>
-    <t>ISIC 241</t>
-  </si>
-  <si>
-    <t>ISIC 242</t>
-  </si>
-  <si>
-    <t>ISIC 25</t>
-  </si>
-  <si>
-    <t>ISIC 26</t>
-  </si>
-  <si>
-    <t>ISIC 27</t>
-  </si>
-  <si>
-    <t>ISIC 28</t>
-  </si>
-  <si>
-    <t>ISIC 29</t>
-  </si>
-  <si>
-    <t>ISIC 30</t>
-  </si>
-  <si>
-    <t>ISIC 31T33</t>
-  </si>
-  <si>
-    <t>ISIC 351</t>
-  </si>
-  <si>
-    <t>ISIC 352T353</t>
-  </si>
-  <si>
-    <t>ISIC 36T39</t>
-  </si>
-  <si>
-    <t>ISIC 41T43</t>
-  </si>
-  <si>
-    <t>ISIC 45T47</t>
-  </si>
-  <si>
-    <t>ISIC 49T53</t>
-  </si>
-  <si>
-    <t>ISIC 55T56</t>
-  </si>
-  <si>
-    <t>ISIC 58T60</t>
-  </si>
-  <si>
-    <t>ISIC 61</t>
-  </si>
-  <si>
-    <t>ISIC 62T63</t>
-  </si>
-  <si>
-    <t>ISIC 64T66</t>
-  </si>
-  <si>
-    <t>ISIC 68</t>
-  </si>
-  <si>
-    <t>ISIC 69T82</t>
-  </si>
-  <si>
-    <t>ISIC 84</t>
-  </si>
-  <si>
-    <t>ISIC 85</t>
-  </si>
-  <si>
-    <t>ISIC 86T88</t>
-  </si>
-  <si>
-    <t>ISIC 90T96</t>
-  </si>
-  <si>
-    <t>Net income</t>
+    <t>Validation checks (42-code sibling)</t>
+  </si>
+  <si>
+    <t>Allocation output rows sum to 1 across the 42 ISIC codes (rate files excluded — see note).</t>
+  </si>
+  <si>
+    <t>VRSbRIC.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  LDVs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  HDVs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  aircraft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  rail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ships</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  motorbike</t>
+  </si>
+  <si>
+    <t>Trauck Manufacturers Industry Average</t>
+  </si>
+  <si>
+    <t>Manufacturing Cost</t>
+  </si>
+  <si>
+    <t>Dealer new vehicle net income</t>
+  </si>
+  <si>
+    <t>Dealer new vehicle selling expense</t>
   </si>
   <si>
     <t>Vehicle Type</t>
@@ -393,55 +484,13 @@
   </si>
   <si>
     <t>motorbike</t>
-  </si>
-  <si>
-    <t>EPA</t>
-  </si>
-  <si>
-    <t>Automobile Industry Retail Price Equivalent and Indirect Cost Multipliers</t>
-  </si>
-  <si>
-    <t>Link</t>
-  </si>
-  <si>
-    <t>Table 3-3</t>
-  </si>
-  <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t>We assume the same cost breakdowns for all technologies, but assign non-road to non-road vehicle manufacturing</t>
-  </si>
-  <si>
-    <t>The RPEF file also controls whether or not these values are used</t>
-  </si>
-  <si>
-    <t>Passenger LDVs</t>
-  </si>
-  <si>
-    <t>Freight LDVs and HDVs and Passenger HDVs</t>
-  </si>
-  <si>
-    <t>Heavy Duty Truck Retail Price Equivalent and Indirect Cost Multipliers</t>
-  </si>
-  <si>
-    <t>Manufacturing Cost</t>
-  </si>
-  <si>
-    <t>Dealer new vehicle net income</t>
-  </si>
-  <si>
-    <t>Dealer new vehicle selling expense</t>
-  </si>
-  <si>
-    <t>Trauck Manufacturers Industry Average</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -464,6 +513,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -491,9 +545,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -502,6 +556,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -540,7 +598,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2911ECC1-C01A-088B-FB30-7772E3FD1E8A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -562,6 +620,9 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -589,7 +650,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8E3DADF-2E71-3D63-AAEB-E30A6A4301EE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -611,6 +672,9 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -914,8 +978,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA6E6C8E-C26C-4C73-93CC-7550EEEA6E9A}">
-  <dimension ref="A1:B22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="69" customWidth="1"/>
@@ -931,12 +995,12 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>126</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>119</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -946,27 +1010,27 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>120</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>122</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>127</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>119</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -976,43 +1040,78 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>128</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>122</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>123</v>
+        <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>124</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>125</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B25" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B26" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B29" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B30" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{E18AB7C8-B002-4830-9F8F-289DE6D1CAE5}"/>
-    <hyperlink ref="B14" r:id="rId2" xr:uid="{16F9FBDF-945F-40A7-8782-6520C8200155}"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B14" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFD20EDD-472C-457D-96DA-E16DAC72FCB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1023,77 +1122,77 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>0.03</v>
       </c>
       <c r="D3">
-        <f>C3/($C$16-$C$2)</f>
+        <f t="shared" ref="D3:D14" si="0">C3/($C$16-$C$2)</f>
         <v>6.5217391304347769E-2</v>
       </c>
       <c r="E3" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>0.05</v>
       </c>
       <c r="D4">
-        <f t="shared" ref="D4:D14" si="0">C4/($C$16-$C$2)</f>
+        <f t="shared" si="0"/>
         <v>0.10869565217391296</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>7.0000000000000007E-2</v>
@@ -1103,15 +1202,15 @@
         <v>0.15217391304347813</v>
       </c>
       <c r="E5" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>0.03</v>
@@ -1121,15 +1220,15 @@
         <v>6.5217391304347769E-2</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>7.0000000000000007E-2</v>
@@ -1139,15 +1238,15 @@
         <v>0.15217391304347813</v>
       </c>
       <c r="E7" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1157,15 +1256,15 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>0.01</v>
@@ -1175,15 +1274,15 @@
         <v>2.1739130434782591E-2</v>
       </c>
       <c r="E9" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C10">
         <v>0.04</v>
@@ -1193,15 +1292,15 @@
         <v>8.6956521739130363E-2</v>
       </c>
       <c r="E10" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C11">
         <v>0.04</v>
@@ -1211,15 +1310,15 @@
         <v>8.6956521739130363E-2</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1229,15 +1328,15 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C13">
         <v>0.06</v>
@@ -1247,15 +1346,15 @@
         <v>0.13043478260869554</v>
       </c>
       <c r="E13" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>45</v>
       </c>
       <c r="C14">
         <v>0.06</v>
@@ -1265,12 +1364,12 @@
         <v>0.13043478260869554</v>
       </c>
       <c r="E14" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C16">
         <f>SUM(C2:C14)</f>
@@ -1279,194 +1378,194 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B37" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="B39" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B42" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B43" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B45" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="B46" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" t="s">
         <v>93</v>
-      </c>
-      <c r="B48" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -1474,143 +1573,143 @@
         <v>94</v>
       </c>
       <c r="B49" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B50" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B51" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B52" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="B53" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B54" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B56" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B57" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B58" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B59" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B60" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B61" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B62" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B63" t="s">
-        <v>65</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="B64" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="B65" t="s">
-        <v>67</v>
+        <v>126</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="B66" t="s">
-        <v>69</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -1620,7 +1719,114 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{289C64CC-E62D-4411-9368-8E9242EA44DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5">
+        <f>SUM(VRSbRIC!B2:AQ2)</f>
+        <v>0.99999999999999911</v>
+      </c>
+      <c r="C5" s="6" t="str">
+        <f t="shared" ref="C5:C10" si="0">IF(ABS(B5-1)&lt;0.000001,"=1",IF(ABS(B5)&lt;0.000001,"=0","CHECK"))</f>
+        <v>=1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6">
+        <f>SUM(VRSbRIC!B3:AQ3)</f>
+        <v>0.99999999999999922</v>
+      </c>
+      <c r="C6" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>=1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7">
+        <f>SUM(VRSbRIC!B4:AQ4)</f>
+        <v>0.99999999999999922</v>
+      </c>
+      <c r="C7" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>=1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B8">
+        <f>SUM(VRSbRIC!B5:AQ5)</f>
+        <v>0.99999999999999922</v>
+      </c>
+      <c r="C8" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>=1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B9">
+        <f>SUM(VRSbRIC!B6:AQ6)</f>
+        <v>0.99999999999999922</v>
+      </c>
+      <c r="C9" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>=1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10">
+        <f>SUM(VRSbRIC!B7:AQ7)</f>
+        <v>0.99999999999999911</v>
+      </c>
+      <c r="C10" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>=1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1631,77 +1837,77 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>0.04</v>
       </c>
       <c r="D3">
-        <f>C3/($C$16-$C$2)</f>
+        <f t="shared" ref="D3:D14" si="0">C3/($C$16-$C$2)</f>
         <v>0.11111111111111102</v>
       </c>
       <c r="E3" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>0.05</v>
       </c>
       <c r="D4">
-        <f t="shared" ref="D4:D14" si="0">C4/($C$16-$C$2)</f>
+        <f t="shared" si="0"/>
         <v>0.13888888888888878</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>0.04</v>
@@ -1711,15 +1917,15 @@
         <v>0.11111111111111102</v>
       </c>
       <c r="E5" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>0.02</v>
@@ -1729,15 +1935,15 @@
         <v>5.5555555555555511E-2</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>7.0000000000000007E-2</v>
@@ -1747,15 +1953,15 @@
         <v>0.19444444444444428</v>
       </c>
       <c r="E7" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <v>0.01</v>
@@ -1765,15 +1971,15 @@
         <v>2.7777777777777755E-2</v>
       </c>
       <c r="E8" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>0.01</v>
@@ -1783,15 +1989,15 @@
         <v>2.7777777777777755E-2</v>
       </c>
       <c r="E9" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1801,15 +2007,15 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C11">
         <v>0.01</v>
@@ -1819,15 +2025,15 @@
         <v>2.7777777777777755E-2</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1837,15 +2043,15 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C13">
         <v>0.06</v>
@@ -1855,15 +2061,15 @@
         <v>0.16666666666666652</v>
       </c>
       <c r="E13" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>45</v>
       </c>
       <c r="C14">
         <v>0.05</v>
@@ -1873,12 +2079,12 @@
         <v>0.13888888888888878</v>
       </c>
       <c r="E14" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C16">
         <f>SUM(C2:C14)</f>
@@ -1887,194 +2093,194 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B37" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="B39" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B42" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B43" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B45" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="B46" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" t="s">
         <v>93</v>
-      </c>
-      <c r="B48" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -2082,143 +2288,143 @@
         <v>94</v>
       </c>
       <c r="B49" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B50" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B51" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B52" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="B53" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B54" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B56" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B57" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B58" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B59" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B60" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B61" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B62" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B63" t="s">
-        <v>65</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="B64" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="B65" t="s">
-        <v>67</v>
+        <v>126</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="B66" t="s">
-        <v>69</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2227,10 +2433,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F95DC9F-CBCD-437C-971E-4F1A6C1AB54A}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
-    <tabColor theme="4" tint="-0.249977111117893"/>
+    <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2240,138 +2446,138 @@
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="B1" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="C1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" t="s">
+        <v>67</v>
+      </c>
+      <c r="M1" t="s">
+        <v>69</v>
+      </c>
+      <c r="N1" t="s">
         <v>71</v>
       </c>
-      <c r="D1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="O1" t="s">
         <v>73</v>
       </c>
-      <c r="F1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="P1" t="s">
         <v>75</v>
       </c>
-      <c r="H1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="Q1" t="s">
         <v>77</v>
       </c>
-      <c r="J1" t="s">
-        <v>78</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="R1" t="s">
         <v>79</v>
       </c>
-      <c r="L1" t="s">
-        <v>80</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="S1" t="s">
         <v>81</v>
       </c>
-      <c r="N1" t="s">
-        <v>82</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="T1" t="s">
         <v>83</v>
       </c>
-      <c r="P1" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="U1" t="s">
         <v>85</v>
       </c>
-      <c r="R1" t="s">
-        <v>86</v>
-      </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
         <v>87</v>
       </c>
-      <c r="T1" t="s">
-        <v>88</v>
-      </c>
-      <c r="U1" t="s">
-        <v>89</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
+        <v>29</v>
+      </c>
+      <c r="X1" t="s">
         <v>90</v>
       </c>
-      <c r="W1" t="s">
-        <v>91</v>
-      </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>92</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>93</v>
       </c>
       <c r="Z1" t="s">
         <v>94</v>
       </c>
       <c r="AA1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AB1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AC1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AD1" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="AE1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AF1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="AG1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="AH1" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="AI1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="AJ1" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="AK1" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="AL1" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="AM1" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="AN1" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="AO1" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="AP1" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="AQ1" t="s">
-        <v>68</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="B2">
         <f>SUMIFS('LDV Data'!$D$3:$D$14,'LDV Data'!$E$3:$E$14,B1)</f>
@@ -2544,7 +2750,7 @@
     </row>
     <row r="3" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="B3">
         <f>SUMIFS('HDV Data'!$D$3:$D$14,'HDV Data'!$E$3:$E$14,B1)</f>
@@ -2717,50 +2923,50 @@
     </row>
     <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="B4">
-        <f t="shared" ref="B4:B7" si="0">B3</f>
+        <f t="shared" ref="B4:K7" si="0">B3</f>
         <v>0</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C3:AQ7" si="1">C3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="L4:U7" si="1">L3</f>
         <v>0</v>
       </c>
       <c r="M4">
@@ -2800,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="V4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="V4:AE7" si="2">V3</f>
         <v>0</v>
       </c>
       <c r="W4" s="4">
@@ -2811,124 +3017,124 @@
         <v>0.80555555555555491</v>
       </c>
       <c r="Y4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="Y4:AH6" si="3">Y3</f>
         <v>0</v>
       </c>
       <c r="Z4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.19444444444444428</v>
       </c>
       <c r="AE4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="AI4:AR6" si="4">AI3</f>
         <v>0</v>
       </c>
       <c r="AJ4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AK4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AL4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AM4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AN4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AO4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AP4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AQ4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L5">
@@ -2972,135 +3178,135 @@
         <v>0</v>
       </c>
       <c r="V5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W5" s="4">
         <v>0</v>
       </c>
       <c r="X5">
-        <f t="shared" si="1"/>
+        <f>X4</f>
         <v>0.80555555555555491</v>
       </c>
       <c r="Y5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.19444444444444428</v>
       </c>
       <c r="AE5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AJ5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AK5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AL5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AM5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AN5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AO5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AP5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AQ5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L6">
@@ -3144,135 +3350,135 @@
         <v>0</v>
       </c>
       <c r="V6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W6" s="4">
         <v>0</v>
       </c>
       <c r="X6">
-        <f t="shared" si="1"/>
+        <f>X5</f>
         <v>0.80555555555555491</v>
       </c>
       <c r="Y6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Z6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AA6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AB6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AD6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.19444444444444428</v>
       </c>
       <c r="AE6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AG6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AI6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AJ6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AK6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AL6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AM6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AN6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AO6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AP6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AQ6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L7">
@@ -3316,7 +3522,7 @@
         <v>0</v>
       </c>
       <c r="V7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W7">
@@ -3327,79 +3533,79 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <f t="shared" si="1"/>
+        <f>Y6</f>
         <v>0</v>
       </c>
       <c r="Z7">
-        <f t="shared" si="1"/>
+        <f>Z6</f>
         <v>0</v>
       </c>
       <c r="AA7">
-        <f t="shared" si="1"/>
+        <f>AA6</f>
         <v>0</v>
       </c>
       <c r="AB7">
-        <f t="shared" si="1"/>
+        <f>AB6</f>
         <v>0</v>
       </c>
       <c r="AC7">
-        <f t="shared" si="1"/>
+        <f>AC6</f>
         <v>0</v>
       </c>
       <c r="AD7">
-        <f t="shared" si="1"/>
-        <v>0.19444444444444428</v>
+        <f>SUMIFS('LDV Data'!$D$3:$D$14,'LDV Data'!$E$3:$E$14,AD1)</f>
+        <v>0.30434782608695626</v>
       </c>
       <c r="AE7">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="AE7:AQ7" si="5">AE6</f>
         <v>0</v>
       </c>
       <c r="AF7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AG7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AH7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AI7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AJ7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AK7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AL7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AM7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AN7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AO7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AP7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AQ7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
